--- a/InputData/io-model/VoSTR/VAT or Sales Tax Rate.xlsx
+++ b/InputData/io-model/VoSTR/VAT or Sales Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan\Documents\state-eps-data-repository\CO\io-model\VoSTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\CO\io-model\VoSTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E35B20E-26E1-4237-8A06-41984499F902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF3CACD0-04CE-46C1-9752-F59F8771915D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2071,7 +2071,7 @@
         <v>346</v>
       </c>
       <c r="C1" s="16">
-        <v>45298</v>
+        <v>46185</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>335</v>
